--- a/EDI_Project_Documentation/FTP-SFTP-Connection Details.xlsx
+++ b/EDI_Project_Documentation/FTP-SFTP-Connection Details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RPAdmin\Desktop\FInal-SOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2228D1C4-119B-46E1-A930-1DFB26355130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E678E12B-78B8-4919-A3D6-52F9C3871BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="138">
   <si>
     <t>No</t>
   </si>
@@ -226,27 +226,6 @@
     <t>j8pL5GNA</t>
   </si>
   <si>
-    <t>FTP &amp; SFTP</t>
-  </si>
-  <si>
-    <t>21 &amp; 22</t>
-  </si>
-  <si>
-    <t>21 &amp; 10022</t>
-  </si>
-  <si>
-    <t>edi-fpl &amp; neeb2b.nee.com</t>
-  </si>
-  <si>
-    <t>rp1211Edi0610 &amp; ce7*ras8</t>
-  </si>
-  <si>
-    <t>edi-pseg &amp; PSEG_Radius_User</t>
-  </si>
-  <si>
-    <t>rp1211Edi0610 &amp; Nr%2*405efbWq</t>
-  </si>
-  <si>
     <t>edi-atmosenergy</t>
   </si>
   <si>
@@ -331,12 +310,6 @@
     <t>RadiusPointHQ.com</t>
   </si>
   <si>
-    <t>RadiusPointHQ.com  &amp; neeb2b.nee.com</t>
-  </si>
-  <si>
-    <t>RadiusPointHQ.com &amp; ftp2.ecinfosystems.com</t>
-  </si>
-  <si>
     <t>Eversource</t>
   </si>
   <si>
@@ -391,9 +364,6 @@
     <t>Calpine Energy</t>
   </si>
   <si>
-    <t>Waiting for SFTP login details</t>
-  </si>
-  <si>
     <t>EDI-Calpine</t>
   </si>
   <si>
@@ -434,13 +404,49 @@
   </si>
   <si>
     <t>New Partner Onboarded - 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SFTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> neeb2b.nee.com</t>
+  </si>
+  <si>
+    <t>PSEG_Radius_User</t>
+  </si>
+  <si>
+    <t>Copy Ack and Archive in FTP</t>
+  </si>
+  <si>
+    <t>fpl_radiuspoint_in</t>
+  </si>
+  <si>
+    <t>ce7*ras8</t>
+  </si>
+  <si>
+    <t>Waiting for files I want to check</t>
+  </si>
+  <si>
+    <t>ftp2.ecinfosystems.com</t>
+  </si>
+  <si>
+    <t>Nr%2*405efbWq</t>
+  </si>
+  <si>
+    <t>Enbridge</t>
+  </si>
+  <si>
+    <t>EDI-Enbridge</t>
+  </si>
+  <si>
+    <t>vABCjbXJazbPrHvv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,8 +525,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,8 +569,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -664,12 +682,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -708,20 +735,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -739,8 +756,26 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1619,7 +1654,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>1</v>
@@ -1638,7 +1673,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1</v>
@@ -1656,7 +1691,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="27" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1678,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5986E5A9-043E-4B27-ABD7-9C6337618BF1}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
@@ -1707,786 +1742,912 @@
       <c r="E1" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="37" t="s">
-        <v>113</v>
+      <c r="G1" s="33" t="s">
+        <v>104</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="21" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="26">
+        <v>93</v>
+      </c>
+      <c r="D2" s="23">
         <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="46">
         <v>22</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>121</v>
+      <c r="G3" s="44" t="s">
+        <v>132</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="26">
+        <v>93</v>
+      </c>
+      <c r="D4" s="23">
         <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="26">
+        <v>93</v>
+      </c>
+      <c r="D5" s="23">
         <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="1"/>
+      <c r="B6" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="49">
+        <v>22</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>132</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="1"/>
+      <c r="B7" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="49">
+        <v>22</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>132</v>
+      </c>
       <c r="H7" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="26">
+        <v>93</v>
+      </c>
+      <c r="D8" s="23">
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H8" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="26">
+        <v>93</v>
+      </c>
+      <c r="D9" s="23">
         <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H9" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="26">
+      <c r="C10" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="46">
         <v>22</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="1"/>
+      <c r="E10" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>132</v>
+      </c>
       <c r="H10" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="26">
+        <v>93</v>
+      </c>
+      <c r="D11" s="23">
         <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H11" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="26">
+        <v>93</v>
+      </c>
+      <c r="D12" s="23">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H12" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="26">
+        <v>93</v>
+      </c>
+      <c r="D13" s="23">
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H13" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="22" t="s">
         <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="26">
+        <v>93</v>
+      </c>
+      <c r="D14" s="23">
         <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H14" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="C15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="26">
+        <v>93</v>
+      </c>
+      <c r="D16" s="23">
         <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="26">
+        <v>93</v>
+      </c>
+      <c r="D17" s="23">
         <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H17" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="26">
+        <v>93</v>
+      </c>
+      <c r="D18" s="23">
         <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H18" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="26">
+        <v>93</v>
+      </c>
+      <c r="D19" s="23">
         <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H19" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="26">
+        <v>93</v>
+      </c>
+      <c r="D20" s="23">
         <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H20" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" s="26">
+        <v>93</v>
+      </c>
+      <c r="D21" s="23">
         <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H21" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="26">
+        <v>93</v>
+      </c>
+      <c r="D22" s="23">
         <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H22" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="23">
+        <v>22</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="26">
+        <v>22</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="35"/>
+      <c r="G24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="36">
+        <v>22</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="36">
+        <v>22</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="28">
+        <v>22</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="26">
+      <c r="B28" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="29">
         <v>22</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="30">
-        <v>22</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" s="40">
-        <v>22</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="40">
-        <v>22</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="32">
-        <v>22</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="33">
-        <v>22</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="33"/>
+      <c r="E28" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="40" t="s">
+        <v>129</v>
+      </c>
       <c r="H28" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="29">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="51">
+        <v>22</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="39">
+        <v>22</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="39">
+        <v>22</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="39">
+        <v>22</v>
+      </c>
+      <c r="E33" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="F33" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B34" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="33">
+      <c r="C34" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="39">
         <v>22</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="33">
-        <v>22</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" s="44">
-        <v>22</v>
-      </c>
-      <c r="E31" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="B32" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="44">
-        <v>22</v>
-      </c>
-      <c r="E32" s="44" t="s">
+      <c r="E34" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="44">
-        <v>22</v>
-      </c>
-      <c r="E33" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44" t="s">
-        <v>118</v>
+      <c r="H34" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="27" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="31" t="s">
-        <v>112</v>
+      <c r="B43" s="16" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="16" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F18" r:id="rId1" xr:uid="{B8B9FC06-5FF1-4741-8069-FFE40609484B}"/>
+    <hyperlink ref="F21" r:id="rId2" xr:uid="{EFDEC6F8-BD5D-4D8F-907E-AE25D7902CB1}"/>
+    <hyperlink ref="F29" r:id="rId3" xr:uid="{D1DAD559-9CBF-46D5-9DA7-C2884D612C67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/EDI_Project_Documentation/FTP-SFTP-Connection Details.xlsx
+++ b/EDI_Project_Documentation/FTP-SFTP-Connection Details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RPAdmin\Desktop\FInal-SOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E678E12B-78B8-4919-A3D6-52F9C3871BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE225E8-16B5-4C03-B813-750FB55D8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="139">
   <si>
     <t>No</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>vABCjbXJazbPrHvv</t>
+  </si>
+  <si>
+    <t>vCT4WsR4EACQa6T8</t>
   </si>
 </sst>
 </file>
@@ -2003,7 +2006,7 @@
         <v>68</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="G11" s="40" t="s">
         <v>129</v>
